--- a/output/yearly_total_coral_cover_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_64_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.272567326956924</v>
+        <v>1.249358811228529</v>
       </c>
       <c r="C3" t="n">
-        <v>4.593093762658709</v>
+        <v>4.61875664764772</v>
       </c>
       <c r="D3" t="n">
-        <v>6.195824581651824</v>
+        <v>6.204689763421173</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06148567126746</v>
+        <v>12.07280522229742</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.419358707871579</v>
+        <v>1.37364659879408</v>
       </c>
       <c r="C4" t="n">
-        <v>5.030418342194832</v>
+        <v>5.085827864738899</v>
       </c>
       <c r="D4" t="n">
-        <v>6.47742777583263</v>
+        <v>6.596827703862212</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92720482589904</v>
+        <v>13.05630216739519</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.620150791070018</v>
+        <v>1.539071038732177</v>
       </c>
       <c r="C5" t="n">
-        <v>5.591574365748752</v>
+        <v>5.68943349386509</v>
       </c>
       <c r="D5" t="n">
-        <v>6.848608852144396</v>
+        <v>6.985115257393553</v>
       </c>
       <c r="E5" t="n">
-        <v>14.06033400896317</v>
+        <v>14.21361978999082</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.837715672599484</v>
+        <v>1.721398351869703</v>
       </c>
       <c r="C6" t="n">
-        <v>6.31078425725781</v>
+        <v>6.401787277298485</v>
       </c>
       <c r="D6" t="n">
-        <v>7.248687986283863</v>
+        <v>7.477764123671639</v>
       </c>
       <c r="E6" t="n">
-        <v>15.39718791614116</v>
+        <v>15.60094975283983</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.082351694991307</v>
+        <v>1.916970474951923</v>
       </c>
       <c r="C7" t="n">
-        <v>7.15011035446257</v>
+        <v>7.229454172596091</v>
       </c>
       <c r="D7" t="n">
-        <v>7.63181082581827</v>
+        <v>8.012802262637022</v>
       </c>
       <c r="E7" t="n">
-        <v>16.86427287527215</v>
+        <v>17.15922691018504</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.291509952440662</v>
+        <v>1.122920721038024</v>
       </c>
       <c r="C8" t="n">
-        <v>4.876108004907773</v>
+        <v>4.804591541166899</v>
       </c>
       <c r="D8" t="n">
-        <v>5.820987836156287</v>
+        <v>6.285570741860863</v>
       </c>
       <c r="E8" t="n">
-        <v>11.98860579350472</v>
+        <v>12.21308300406579</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.621509088790533</v>
+        <v>1.372699022693848</v>
       </c>
       <c r="C9" t="n">
-        <v>5.972792811572646</v>
+        <v>5.748776916657175</v>
       </c>
       <c r="D9" t="n">
-        <v>6.422339892213735</v>
+        <v>6.95903741811432</v>
       </c>
       <c r="E9" t="n">
-        <v>14.01664179257691</v>
+        <v>14.08051335746534</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.972612303681498</v>
+        <v>1.63154014657941</v>
       </c>
       <c r="C10" t="n">
-        <v>7.234155439291512</v>
+        <v>6.776737269877766</v>
       </c>
       <c r="D10" t="n">
-        <v>7.013225755096205</v>
+        <v>7.601997926698242</v>
       </c>
       <c r="E10" t="n">
-        <v>16.21999349806921</v>
+        <v>16.01027534315542</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.319938192818085</v>
+        <v>1.901834061848715</v>
       </c>
       <c r="C11" t="n">
-        <v>8.601619890494648</v>
+        <v>7.894055348253729</v>
       </c>
       <c r="D11" t="n">
-        <v>7.57690262474848</v>
+        <v>8.253996962728683</v>
       </c>
       <c r="E11" t="n">
-        <v>18.49846070806121</v>
+        <v>18.04988637283112</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.669539588311502</v>
+        <v>2.183100639206214</v>
       </c>
       <c r="C12" t="n">
-        <v>10.00846530698637</v>
+        <v>9.084327402484689</v>
       </c>
       <c r="D12" t="n">
-        <v>8.120173475278003</v>
+        <v>8.972577907048105</v>
       </c>
       <c r="E12" t="n">
-        <v>20.79817837057587</v>
+        <v>20.24000594873901</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.004314303396366</v>
+        <v>2.478764818285333</v>
       </c>
       <c r="C13" t="n">
-        <v>11.45205951534176</v>
+        <v>10.38927428367179</v>
       </c>
       <c r="D13" t="n">
-        <v>8.636826542455145</v>
+        <v>9.666139542880677</v>
       </c>
       <c r="E13" t="n">
-        <v>23.09320036119327</v>
+        <v>22.5341786448378</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.734168962258608</v>
+        <v>1.453408753798106</v>
       </c>
       <c r="C14" t="n">
-        <v>8.004336294879883</v>
+        <v>7.447145385334604</v>
       </c>
       <c r="D14" t="n">
-        <v>6.53722234313049</v>
+        <v>7.292706653979539</v>
       </c>
       <c r="E14" t="n">
-        <v>16.27572760026898</v>
+        <v>16.19326079311225</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.770464174884613</v>
+        <v>1.488810576013246</v>
       </c>
       <c r="C15" t="n">
-        <v>8.560476734381616</v>
+        <v>7.930371422841927</v>
       </c>
       <c r="D15" t="n">
-        <v>6.586761332286785</v>
+        <v>7.438604180307658</v>
       </c>
       <c r="E15" t="n">
-        <v>16.91770224155302</v>
+        <v>16.85778617916283</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.052569377699934</v>
+        <v>1.725617939754619</v>
       </c>
       <c r="C16" t="n">
-        <v>10.03077154869277</v>
+        <v>9.337687121925645</v>
       </c>
       <c r="D16" t="n">
-        <v>7.147476716090308</v>
+        <v>8.115293420413856</v>
       </c>
       <c r="E16" t="n">
-        <v>19.23081764248301</v>
+        <v>19.17859848209412</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.643975800669454</v>
+        <v>1.38194733840598</v>
       </c>
       <c r="C17" t="n">
-        <v>9.180921648511514</v>
+        <v>8.599766277505573</v>
       </c>
       <c r="D17" t="n">
-        <v>6.690080460681719</v>
+        <v>7.674125454556467</v>
       </c>
       <c r="E17" t="n">
-        <v>17.51497790986269</v>
+        <v>17.65583907046802</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.876532196851439</v>
+        <v>1.576971519854609</v>
       </c>
       <c r="C18" t="n">
-        <v>10.64071176238722</v>
+        <v>10.02613769952872</v>
       </c>
       <c r="D18" t="n">
-        <v>7.200913243632463</v>
+        <v>8.301216800644118</v>
       </c>
       <c r="E18" t="n">
-        <v>19.71815720287113</v>
+        <v>19.90432602002745</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.88624168164644</v>
+        <v>1.583559046950105</v>
       </c>
       <c r="C19" t="n">
-        <v>11.32432232380837</v>
+        <v>10.71571728699168</v>
       </c>
       <c r="D19" t="n">
-        <v>7.348283391516951</v>
+        <v>8.513382297008896</v>
       </c>
       <c r="E19" t="n">
-        <v>20.55884739697176</v>
+        <v>20.81265863095068</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.115931374532023</v>
+        <v>1.768353417320482</v>
       </c>
       <c r="C20" t="n">
-        <v>12.98941551759617</v>
+        <v>12.32543009278292</v>
       </c>
       <c r="D20" t="n">
-        <v>7.952195674307334</v>
+        <v>9.17632706925564</v>
       </c>
       <c r="E20" t="n">
-        <v>23.05754256643553</v>
+        <v>23.27011057935905</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.2711276575506</v>
+        <v>1.054770098488688</v>
       </c>
       <c r="C21" t="n">
-        <v>9.54880214824688</v>
+        <v>9.1272396840433</v>
       </c>
       <c r="D21" t="n">
-        <v>6.672065390308791</v>
+        <v>7.725834106139147</v>
       </c>
       <c r="E21" t="n">
-        <v>17.49199519610627</v>
+        <v>17.90784388867113</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_64_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249358811228529</v>
+        <v>1.24924100150402</v>
       </c>
       <c r="C3" t="n">
-        <v>4.61875664764772</v>
+        <v>4.589068597071297</v>
       </c>
       <c r="D3" t="n">
-        <v>6.204689763421173</v>
+        <v>6.039402719934179</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07280522229742</v>
+        <v>11.8777123185095</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.37364659879408</v>
+        <v>1.367318371778938</v>
       </c>
       <c r="C4" t="n">
-        <v>5.085827864738899</v>
+        <v>5.020648292516928</v>
       </c>
       <c r="D4" t="n">
-        <v>6.596827703862212</v>
+        <v>6.230384496728975</v>
       </c>
       <c r="E4" t="n">
-        <v>13.05630216739519</v>
+        <v>12.61835116102484</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.539071038732177</v>
+        <v>1.539565938085155</v>
       </c>
       <c r="C5" t="n">
-        <v>5.68943349386509</v>
+        <v>5.551991121664534</v>
       </c>
       <c r="D5" t="n">
-        <v>6.985115257393553</v>
+        <v>6.522619928489925</v>
       </c>
       <c r="E5" t="n">
-        <v>14.21361978999082</v>
+        <v>13.61417698823961</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.721398351869703</v>
+        <v>1.734764236519913</v>
       </c>
       <c r="C6" t="n">
-        <v>6.401787277298485</v>
+        <v>6.192971217124592</v>
       </c>
       <c r="D6" t="n">
-        <v>7.477764123671639</v>
+        <v>6.847731374721299</v>
       </c>
       <c r="E6" t="n">
-        <v>15.60094975283983</v>
+        <v>14.7754668283658</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.916970474951923</v>
+        <v>1.959091237851002</v>
       </c>
       <c r="C7" t="n">
-        <v>7.229454172596091</v>
+        <v>6.965703368584822</v>
       </c>
       <c r="D7" t="n">
-        <v>8.012802262637022</v>
+        <v>7.204137657876577</v>
       </c>
       <c r="E7" t="n">
-        <v>17.15922691018504</v>
+        <v>16.1289322643124</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.122920721038024</v>
+        <v>1.196690984435318</v>
       </c>
       <c r="C8" t="n">
-        <v>4.804591541166899</v>
+        <v>4.652025790824351</v>
       </c>
       <c r="D8" t="n">
-        <v>6.285570741860863</v>
+        <v>5.511496828837478</v>
       </c>
       <c r="E8" t="n">
-        <v>12.21308300406579</v>
+        <v>11.36021360409715</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.372699022693848</v>
+        <v>1.509523112694795</v>
       </c>
       <c r="C9" t="n">
-        <v>5.748776916657175</v>
+        <v>5.715890669061221</v>
       </c>
       <c r="D9" t="n">
-        <v>6.95903741811432</v>
+        <v>5.995944743662384</v>
       </c>
       <c r="E9" t="n">
-        <v>14.08051335746534</v>
+        <v>13.2213585254184</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.63154014657941</v>
+        <v>1.850658161454297</v>
       </c>
       <c r="C10" t="n">
-        <v>6.776737269877766</v>
+        <v>6.97979027241717</v>
       </c>
       <c r="D10" t="n">
-        <v>7.601997926698242</v>
+        <v>6.534605910846957</v>
       </c>
       <c r="E10" t="n">
-        <v>16.01027534315542</v>
+        <v>15.36505434471842</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.901834061848715</v>
+        <v>2.198463782909459</v>
       </c>
       <c r="C11" t="n">
-        <v>7.894055348253729</v>
+        <v>8.355154275441185</v>
       </c>
       <c r="D11" t="n">
-        <v>8.253996962728683</v>
+        <v>7.079764520039248</v>
       </c>
       <c r="E11" t="n">
-        <v>18.04988637283112</v>
+        <v>17.63338257838989</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.183100639206214</v>
+        <v>2.541395686066601</v>
       </c>
       <c r="C12" t="n">
-        <v>9.084327402484689</v>
+        <v>9.839427648414025</v>
       </c>
       <c r="D12" t="n">
-        <v>8.972577907048105</v>
+        <v>7.728529481030205</v>
       </c>
       <c r="E12" t="n">
-        <v>20.24000594873901</v>
+        <v>20.10935281551083</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.478764818285333</v>
+        <v>2.876415778425272</v>
       </c>
       <c r="C13" t="n">
-        <v>10.38927428367179</v>
+        <v>11.37569779276205</v>
       </c>
       <c r="D13" t="n">
-        <v>9.666139542880677</v>
+        <v>8.319680233043897</v>
       </c>
       <c r="E13" t="n">
-        <v>22.5341786448378</v>
+        <v>22.57179380423122</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.453408753798106</v>
+        <v>1.660459344623758</v>
       </c>
       <c r="C14" t="n">
-        <v>7.447145385334604</v>
+        <v>7.961875706671208</v>
       </c>
       <c r="D14" t="n">
-        <v>7.292706653979539</v>
+        <v>6.385630680117742</v>
       </c>
       <c r="E14" t="n">
-        <v>16.19326079311225</v>
+        <v>16.00796573141271</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.488810576013246</v>
+        <v>1.697746122431052</v>
       </c>
       <c r="C15" t="n">
-        <v>7.930371422841927</v>
+        <v>8.636974515496526</v>
       </c>
       <c r="D15" t="n">
-        <v>7.438604180307658</v>
+        <v>6.473929068637699</v>
       </c>
       <c r="E15" t="n">
-        <v>16.85778617916283</v>
+        <v>16.80864970656528</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.725617939754619</v>
+        <v>1.972115153336908</v>
       </c>
       <c r="C16" t="n">
-        <v>9.337687121925645</v>
+        <v>10.23747852782193</v>
       </c>
       <c r="D16" t="n">
-        <v>8.115293420413856</v>
+        <v>6.994225899457382</v>
       </c>
       <c r="E16" t="n">
-        <v>19.17859848209412</v>
+        <v>19.20381958061622</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.38194733840598</v>
+        <v>1.584177548003781</v>
       </c>
       <c r="C17" t="n">
-        <v>8.599766277505573</v>
+        <v>9.507598197099641</v>
       </c>
       <c r="D17" t="n">
-        <v>7.674125454556467</v>
+        <v>6.561550051241728</v>
       </c>
       <c r="E17" t="n">
-        <v>17.65583907046802</v>
+        <v>17.65332579634515</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.576971519854609</v>
+        <v>1.809321749018702</v>
       </c>
       <c r="C18" t="n">
-        <v>10.02613769952872</v>
+        <v>11.12643143906334</v>
       </c>
       <c r="D18" t="n">
-        <v>8.301216800644118</v>
+        <v>7.05058803515819</v>
       </c>
       <c r="E18" t="n">
-        <v>19.90432602002745</v>
+        <v>19.98634122324023</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.583559046950105</v>
+        <v>1.818933059043278</v>
       </c>
       <c r="C19" t="n">
-        <v>10.71571728699168</v>
+        <v>11.93866076721785</v>
       </c>
       <c r="D19" t="n">
-        <v>8.513382297008896</v>
+        <v>7.206568110408924</v>
       </c>
       <c r="E19" t="n">
-        <v>20.81265863095068</v>
+        <v>20.96416193667005</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.768353417320482</v>
+        <v>2.037381740715236</v>
       </c>
       <c r="C20" t="n">
-        <v>12.32543009278292</v>
+        <v>13.76239457253489</v>
       </c>
       <c r="D20" t="n">
-        <v>9.17632706925564</v>
+        <v>7.738979707899013</v>
       </c>
       <c r="E20" t="n">
-        <v>23.27011057935905</v>
+        <v>23.53875602114914</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.054770098488688</v>
+        <v>1.220773817799781</v>
       </c>
       <c r="C21" t="n">
-        <v>9.1272396840433</v>
+        <v>10.13930375739725</v>
       </c>
       <c r="D21" t="n">
-        <v>7.725834106139147</v>
+        <v>6.499768668213476</v>
       </c>
       <c r="E21" t="n">
-        <v>17.90784388867113</v>
+        <v>17.85984624341051</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_64_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.24924100150402</v>
+        <v>2.635658313566771</v>
       </c>
       <c r="C3" t="n">
-        <v>4.589068597071297</v>
+        <v>7.748215123152479</v>
       </c>
       <c r="D3" t="n">
-        <v>6.039402719934179</v>
+        <v>8.113101928090808</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8777123185095</v>
+        <v>18.49697536481006</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.367318371778938</v>
+        <v>1.158393804284538</v>
       </c>
       <c r="C4" t="n">
-        <v>5.020648292516928</v>
+        <v>4.641596362909461</v>
       </c>
       <c r="D4" t="n">
-        <v>6.230384496728975</v>
+        <v>5.604522769895358</v>
       </c>
       <c r="E4" t="n">
-        <v>12.61835116102484</v>
+        <v>11.40451293708936</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.539565938085155</v>
+        <v>1.325629515451132</v>
       </c>
       <c r="C5" t="n">
-        <v>5.551991121664534</v>
+        <v>5.470194984020001</v>
       </c>
       <c r="D5" t="n">
-        <v>6.522619928489925</v>
+        <v>5.852071608587369</v>
       </c>
       <c r="E5" t="n">
-        <v>13.61417698823961</v>
+        <v>12.6478961080585</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.734764236519913</v>
+        <v>1.505309885382419</v>
       </c>
       <c r="C6" t="n">
-        <v>6.192971217124592</v>
+        <v>6.547753343664655</v>
       </c>
       <c r="D6" t="n">
-        <v>6.847731374721299</v>
+        <v>6.188686536984108</v>
       </c>
       <c r="E6" t="n">
-        <v>14.7754668283658</v>
+        <v>14.24174976603118</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.959091237851002</v>
+        <v>1.690989051244395</v>
       </c>
       <c r="C7" t="n">
-        <v>6.965703368584822</v>
+        <v>7.819015870659241</v>
       </c>
       <c r="D7" t="n">
-        <v>7.204137657876577</v>
+        <v>6.508227675908925</v>
       </c>
       <c r="E7" t="n">
-        <v>16.1289322643124</v>
+        <v>16.01823259781256</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.196690984435318</v>
+        <v>1.876221890315279</v>
       </c>
       <c r="C8" t="n">
-        <v>4.652025790824351</v>
+        <v>9.262870293690201</v>
       </c>
       <c r="D8" t="n">
-        <v>5.511496828837478</v>
+        <v>6.837537474672629</v>
       </c>
       <c r="E8" t="n">
-        <v>11.36021360409715</v>
+        <v>17.97662965867811</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.509523112694795</v>
+        <v>2.042654777827973</v>
       </c>
       <c r="C9" t="n">
-        <v>5.715890669061221</v>
+        <v>10.93300324677784</v>
       </c>
       <c r="D9" t="n">
-        <v>5.995944743662384</v>
+        <v>7.150055101143939</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2213585254184</v>
+        <v>20.12571312574975</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.850658161454297</v>
+        <v>1.236619225746325</v>
       </c>
       <c r="C10" t="n">
-        <v>6.97979027241717</v>
+        <v>7.9480036116102</v>
       </c>
       <c r="D10" t="n">
-        <v>6.534605910846957</v>
+        <v>5.63184479279704</v>
       </c>
       <c r="E10" t="n">
-        <v>15.36505434471842</v>
+        <v>14.81646763015356</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.198463782909459</v>
+        <v>1.182691824352047</v>
       </c>
       <c r="C11" t="n">
-        <v>8.355154275441185</v>
+        <v>8.79502607840322</v>
       </c>
       <c r="D11" t="n">
-        <v>7.079764520039248</v>
+        <v>5.430203631821788</v>
       </c>
       <c r="E11" t="n">
-        <v>17.63338257838989</v>
+        <v>15.40792153457706</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.541395686066601</v>
+        <v>1.286403651828681</v>
       </c>
       <c r="C12" t="n">
-        <v>9.839427648414025</v>
+        <v>10.66353739651096</v>
       </c>
       <c r="D12" t="n">
-        <v>7.728529481030205</v>
+        <v>5.765676639839965</v>
       </c>
       <c r="E12" t="n">
-        <v>20.10935281551083</v>
+        <v>17.71561768817961</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.876415778425272</v>
+        <v>1.010257657578138</v>
       </c>
       <c r="C13" t="n">
-        <v>11.37569779276205</v>
+        <v>10.33014569362579</v>
       </c>
       <c r="D13" t="n">
-        <v>8.319680233043897</v>
+        <v>5.204107135533747</v>
       </c>
       <c r="E13" t="n">
-        <v>22.57179380423122</v>
+        <v>16.54451048673767</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.660459344623758</v>
+        <v>1.093254608495163</v>
       </c>
       <c r="C14" t="n">
-        <v>7.961875706671208</v>
+        <v>12.25601071261563</v>
       </c>
       <c r="D14" t="n">
-        <v>6.385630680117742</v>
+        <v>5.534347428288289</v>
       </c>
       <c r="E14" t="n">
-        <v>16.00796573141271</v>
+        <v>18.88361274939908</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.697746122431052</v>
+        <v>1.053601818720635</v>
       </c>
       <c r="C15" t="n">
-        <v>8.636974515496526</v>
+        <v>13.34086156076244</v>
       </c>
       <c r="D15" t="n">
-        <v>6.473929068637699</v>
+        <v>5.534818667186328</v>
       </c>
       <c r="E15" t="n">
-        <v>16.80864970656528</v>
+        <v>19.9292820466694</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.972115153336908</v>
+        <v>1.138817519449258</v>
       </c>
       <c r="C16" t="n">
-        <v>10.23747852782193</v>
+        <v>15.5073823944943</v>
       </c>
       <c r="D16" t="n">
-        <v>6.994225899457382</v>
+        <v>5.913557296530663</v>
       </c>
       <c r="E16" t="n">
-        <v>19.20381958061622</v>
+        <v>22.55975721047422</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.584177548003781</v>
+        <v>0.6701606178729577</v>
       </c>
       <c r="C17" t="n">
-        <v>9.507598197099641</v>
+        <v>11.47505004884138</v>
       </c>
       <c r="D17" t="n">
-        <v>6.561550051241728</v>
+        <v>4.9010514367098</v>
       </c>
       <c r="E17" t="n">
-        <v>17.65332579634515</v>
+        <v>17.04626210342413</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.809321749018702</v>
+        <v>0.5248815925985147</v>
       </c>
       <c r="C18" t="n">
-        <v>11.12643143906334</v>
+        <v>10.36568496051953</v>
       </c>
       <c r="D18" t="n">
-        <v>7.05058803515819</v>
+        <v>4.435202333567646</v>
       </c>
       <c r="E18" t="n">
-        <v>19.98634122324023</v>
+        <v>15.32576888668568</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.818933059043278</v>
+        <v>0.6057481509973245</v>
       </c>
       <c r="C19" t="n">
-        <v>11.93866076721785</v>
+        <v>12.75326592481664</v>
       </c>
       <c r="D19" t="n">
-        <v>7.206568110408924</v>
+        <v>4.886128871605249</v>
       </c>
       <c r="E19" t="n">
-        <v>20.96416193667005</v>
+        <v>18.24514294741921</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.037381740715236</v>
+        <v>0.6852500800872312</v>
       </c>
       <c r="C20" t="n">
-        <v>13.76239457253489</v>
+        <v>15.22194906696158</v>
       </c>
       <c r="D20" t="n">
-        <v>7.738979707899013</v>
+        <v>5.304009781917903</v>
       </c>
       <c r="E20" t="n">
-        <v>23.53875602114914</v>
+        <v>21.21120892896671</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.220773817799781</v>
+        <v>0.754728365116778</v>
       </c>
       <c r="C21" t="n">
-        <v>10.13930375739725</v>
+        <v>17.746915804991</v>
       </c>
       <c r="D21" t="n">
-        <v>6.499768668213476</v>
+        <v>5.674305381005715</v>
       </c>
       <c r="E21" t="n">
-        <v>17.85984624341051</v>
+        <v>24.17594955111349</v>
       </c>
     </row>
   </sheetData>
